--- a/data/obx_xlsx/MGN.OL.xlsx
+++ b/data/obx_xlsx/MGN.OL.xlsx
@@ -1554,7 +1554,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1638,6 +1638,12 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -11790,9 +11796,15 @@
       <c r="E61" s="15">
         <v>15.3</v>
       </c>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="17"/>
+      <c r="F61" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="G61" s="28">
+        <v>0.0</v>
+      </c>
+      <c r="H61" s="28">
+        <v>0.0</v>
+      </c>
       <c r="I61" s="17">
         <v>0.0</v>
       </c>
@@ -11812,16 +11824,41 @@
         <v>4.25</v>
       </c>
       <c r="O61" s="15">
-        <v>5.56</v>
-      </c>
-      <c r="P61" s="17"/>
-      <c r="Q61" s="17"/>
-      <c r="R61" s="17"/>
-      <c r="S61" s="17"/>
-      <c r="T61" s="17"/>
-      <c r="U61" s="17"/>
-      <c r="V61" s="17"/>
-      <c r="W61" s="17"/>
+        <f>5.56+O71</f>
+        <v>239.21</v>
+      </c>
+      <c r="P61" s="15">
+        <f t="shared" ref="P61:U61" si="1">P76+P78+P79</f>
+        <v>374.73</v>
+      </c>
+      <c r="Q61" s="15">
+        <f t="shared" si="1"/>
+        <v>13925.08</v>
+      </c>
+      <c r="R61" s="15">
+        <f t="shared" si="1"/>
+        <v>11919.45</v>
+      </c>
+      <c r="S61" s="15">
+        <f t="shared" si="1"/>
+        <v>12318.39</v>
+      </c>
+      <c r="T61" s="15">
+        <f t="shared" si="1"/>
+        <v>6130.08</v>
+      </c>
+      <c r="U61" s="15">
+        <f t="shared" si="1"/>
+        <v>3201.8</v>
+      </c>
+      <c r="V61" s="15">
+        <f t="shared" ref="V61:W61" si="2">V76+V78+V79+V71</f>
+        <v>980.32</v>
+      </c>
+      <c r="W61" s="15">
+        <f t="shared" si="2"/>
+        <v>95.47</v>
+      </c>
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
@@ -12819,7 +12856,9 @@
       <c r="S86" s="15">
         <v>96.99</v>
       </c>
-      <c r="T86" s="17"/>
+      <c r="T86" s="29">
+        <v>26.72</v>
+      </c>
       <c r="U86" s="17"/>
       <c r="V86" s="17"/>
       <c r="W86" s="17"/>
@@ -22211,2472 +22250,2472 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="30" t="s">
         <v>420</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="32" t="s">
         <v>420</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="33">
         <v>1111.64</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="33">
         <v>1555.35</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="33">
         <v>1369.26</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="33">
         <v>1033.58</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="33">
         <v>739.15</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="33">
         <v>1059.38</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="33">
         <v>212.03</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="33">
         <v>127.16</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="33">
         <v>236.93</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="33">
         <v>304.28</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="33">
         <v>259.84</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="33">
         <v>459.07</v>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="33">
         <v>517.97</v>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="33">
         <v>276.01</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="34">
         <v>24.75</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="33">
         <v>9621.84</v>
       </c>
-      <c r="R21" s="33">
+      <c r="R21" s="35">
         <v>15630.69</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="33">
         <v>7444.51</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="35">
         <v>11396.25</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="33">
         <v>3452.11</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="33">
         <v>1879.17</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="33">
         <v>281.12</v>
       </c>
-      <c r="X21" s="33"/>
+      <c r="X21" s="35"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="32" t="s">
         <v>421</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="33">
         <v>1161.79</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="33">
         <v>1151.34</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="33">
         <v>882.68</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="33">
         <v>634.26</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="33">
         <v>474.93</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="33">
         <v>387.95</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="33">
         <v>228.04</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="33">
         <v>277.45</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="33">
         <v>355.62</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="33">
         <v>363.43</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="33">
         <v>307.53</v>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="33">
         <v>2179.93</v>
       </c>
-      <c r="N22" s="31">
+      <c r="N22" s="33">
         <v>5214.25</v>
       </c>
-      <c r="O22" s="31">
+      <c r="O22" s="33">
         <v>6599.56</v>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="33">
         <v>8823.61</v>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="33">
         <v>9509.08</v>
       </c>
-      <c r="R22" s="31">
+      <c r="R22" s="33">
         <v>7960.55</v>
       </c>
-      <c r="S22" s="31">
+      <c r="S22" s="33">
         <v>4890.63</v>
       </c>
-      <c r="T22" s="33"/>
-      <c r="U22" s="33"/>
-      <c r="V22" s="33"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="33"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="35"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="30" t="s">
         <v>422</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="32" t="s">
         <v>422</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="33">
         <v>1290.64</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="33">
         <v>1825.45</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="33">
         <v>1719.86</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="33">
         <v>1104.88</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="33">
         <v>835.95</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="33">
         <v>1123.78</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="33">
         <v>282.83</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="33">
         <v>227.46</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="33">
         <v>434.13</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="33">
         <v>508.98</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="33">
         <v>517.96</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="33">
         <v>598.8</v>
       </c>
-      <c r="N24" s="31">
+      <c r="N24" s="33">
         <v>748.49</v>
       </c>
-      <c r="O24" s="31">
+      <c r="O24" s="33">
         <v>604.78</v>
       </c>
-      <c r="P24" s="31">
+      <c r="P24" s="33">
         <v>149.66</v>
       </c>
-      <c r="Q24" s="31">
+      <c r="Q24" s="33">
         <v>1947.58</v>
       </c>
-      <c r="R24" s="31">
+      <c r="R24" s="33">
         <v>3041.88</v>
       </c>
-      <c r="S24" s="31">
+      <c r="S24" s="33">
         <v>825.99</v>
       </c>
-      <c r="T24" s="31">
+      <c r="T24" s="33">
         <v>8280.05</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="33">
         <v>2799.4</v>
       </c>
-      <c r="V24" s="31">
+      <c r="V24" s="33">
         <v>1613.9</v>
       </c>
-      <c r="W24" s="31">
+      <c r="W24" s="33">
         <v>346.46</v>
       </c>
-      <c r="X24" s="33"/>
+      <c r="X24" s="35"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="32" t="s">
         <v>423</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="33">
         <v>1355.35</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="33">
         <v>1321.98</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="33">
         <v>1013.46</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="33">
         <v>714.98</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="33">
         <v>580.83</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="33">
         <v>515.43</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="33">
         <v>394.27</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="33">
         <v>457.46</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="33">
         <v>561.67</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="33">
         <v>595.8</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="33">
         <v>523.94</v>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="33">
         <v>809.86</v>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="33">
         <v>1298.48</v>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="33">
         <v>1313.98</v>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="33">
         <v>2849.03</v>
       </c>
-      <c r="Q25" s="31">
+      <c r="Q25" s="33">
         <v>3378.98</v>
       </c>
-      <c r="R25" s="31">
+      <c r="R25" s="33">
         <v>3312.24</v>
       </c>
-      <c r="S25" s="31">
+      <c r="S25" s="33">
         <v>2773.16</v>
       </c>
-      <c r="T25" s="33"/>
-      <c r="U25" s="33"/>
-      <c r="V25" s="33"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="33"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="35"/>
+      <c r="X25" s="35"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="30" t="s">
         <v>424</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="32" t="s">
         <v>425</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="34">
         <v>19.62</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="34">
         <v>27.75</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="34">
         <v>25.74</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="34">
         <v>16.53</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="34">
         <v>14.65</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="34">
         <v>21.37</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="34">
         <v>5.38</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="34">
         <v>4.32</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="34">
         <v>4.98</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="34">
         <v>5.84</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="34">
         <v>5.94</v>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="34">
         <v>6.87</v>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="34">
         <v>8.59</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="34">
         <v>6.94</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="34">
         <v>2.86</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="33">
         <v>114.63</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="33">
         <v>179.03</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="33">
         <v>124.19</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="33">
         <v>1376.13</v>
       </c>
-      <c r="U27" s="31">
+      <c r="U27" s="33">
         <v>570.59</v>
       </c>
-      <c r="V27" s="31">
+      <c r="V27" s="33">
         <v>507.06</v>
       </c>
-      <c r="W27" s="31">
+      <c r="W27" s="33">
         <v>152.45</v>
       </c>
-      <c r="X27" s="33"/>
+      <c r="X27" s="35"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="32" t="s">
         <v>426</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="34">
         <v>20.86</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="34">
         <v>21.21</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="34">
         <v>16.73</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="34">
         <v>12.45</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="34">
         <v>10.14</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="34">
         <v>8.38</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="34">
         <v>5.29</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="34">
         <v>5.59</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="34">
         <v>6.44</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="34">
         <v>6.83</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="34">
         <v>6.24</v>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="34">
         <v>27.98</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="34">
         <v>62.41</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="34">
         <v>85.53</v>
       </c>
-      <c r="P28" s="31">
+      <c r="P28" s="33">
         <v>359.37</v>
       </c>
-      <c r="Q28" s="31">
+      <c r="Q28" s="33">
         <v>472.91</v>
       </c>
-      <c r="R28" s="31">
+      <c r="R28" s="33">
         <v>551.4</v>
       </c>
-      <c r="S28" s="31">
+      <c r="S28" s="33">
         <v>546.08</v>
       </c>
-      <c r="T28" s="33"/>
-      <c r="U28" s="33"/>
-      <c r="V28" s="33"/>
-      <c r="W28" s="33"/>
-      <c r="X28" s="33"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="35"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="30" t="s">
         <v>427</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="32" t="s">
         <v>428</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="36">
         <v>-0.78</v>
       </c>
-      <c r="C30" s="34">
+      <c r="C30" s="36">
         <v>-22.59</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="37">
         <v>1.25</v>
       </c>
-      <c r="E30" s="34">
+      <c r="E30" s="36">
         <v>-7.14</v>
       </c>
-      <c r="F30" s="34">
+      <c r="F30" s="36">
         <v>-2.86</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="37">
         <v>2.66</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="37">
         <v>9.02</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="37">
         <v>11.65</v>
       </c>
-      <c r="J30" s="34">
+      <c r="J30" s="36">
         <v>-4.15</v>
       </c>
-      <c r="K30" s="34">
+      <c r="K30" s="36">
         <v>-14.93</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="36">
         <v>-10.43</v>
       </c>
-      <c r="M30" s="34">
+      <c r="M30" s="36">
         <v>-11.69</v>
       </c>
-      <c r="N30" s="35">
+      <c r="N30" s="37">
         <v>1.88</v>
       </c>
-      <c r="O30" s="35">
+      <c r="O30" s="37">
         <v>38.94</v>
       </c>
-      <c r="P30" s="34">
+      <c r="P30" s="36">
         <v>-323.57</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="36">
         <v>-62.87</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="36">
         <v>-107.53</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="36">
         <v>-533.56</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="36">
         <v>-66.5</v>
       </c>
-      <c r="U30" s="34">
+      <c r="U30" s="36">
         <v>-0.04</v>
       </c>
-      <c r="V30" s="34">
+      <c r="V30" s="36">
         <v>-66.21</v>
       </c>
-      <c r="W30" s="34">
+      <c r="W30" s="36">
         <v>-40.99</v>
       </c>
-      <c r="X30" s="35"/>
+      <c r="X30" s="37"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="32" t="s">
         <v>429</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="36">
         <v>-7.38</v>
       </c>
-      <c r="C31" s="34">
+      <c r="C31" s="36">
         <v>-6.58</v>
       </c>
-      <c r="D31" s="34">
+      <c r="D31" s="36">
         <v>-0.27</v>
       </c>
-      <c r="E31" s="34">
+      <c r="E31" s="36">
         <v>-0.07</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="37">
         <v>1.84</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="37">
         <v>1.14</v>
       </c>
-      <c r="H31" s="34">
+      <c r="H31" s="36">
         <v>-2.68</v>
       </c>
-      <c r="I31" s="34">
+      <c r="I31" s="36">
         <v>-7.14</v>
       </c>
-      <c r="J31" s="34">
+      <c r="J31" s="36">
         <v>-7.26</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="37">
         <v>1.67</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="36">
         <v>-25.05</v>
       </c>
-      <c r="M31" s="34">
+      <c r="M31" s="36">
         <v>-56.67</v>
       </c>
-      <c r="N31" s="34">
+      <c r="N31" s="36">
         <v>-86.84</v>
       </c>
-      <c r="O31" s="34">
+      <c r="O31" s="36">
         <v>-218.35</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="36">
         <v>-103.04</v>
       </c>
-      <c r="Q31" s="34">
+      <c r="Q31" s="36">
         <v>-77.92</v>
       </c>
-      <c r="R31" s="34">
+      <c r="R31" s="36">
         <v>-76.39</v>
       </c>
-      <c r="S31" s="34">
+      <c r="S31" s="36">
         <v>-72.38</v>
       </c>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
+      <c r="T31" s="37"/>
+      <c r="U31" s="37"/>
+      <c r="V31" s="37"/>
+      <c r="W31" s="37"/>
+      <c r="X31" s="37"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="30" t="s">
         <v>430</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="32" t="s">
         <v>431</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="37">
         <v>2.86</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="37">
         <v>2.02</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="37">
         <v>1.45</v>
       </c>
-      <c r="E33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="F33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="G33" s="35">
+      <c r="E33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="F33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="G33" s="37">
         <v>0.75</v>
       </c>
-      <c r="H33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="I33" s="35">
+      <c r="H33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I33" s="37">
         <v>64.48</v>
       </c>
-      <c r="J33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="K33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="M33" s="35">
+      <c r="J33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="K33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="L33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="M33" s="37">
         <v>7.7</v>
       </c>
-      <c r="N33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="O33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="P33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="Q33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="R33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="S33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="T33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="U33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="V33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="W33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="X33" s="35"/>
+      <c r="N33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="P33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="Q33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="R33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="S33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="T33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="U33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="V33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="W33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="X33" s="37"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="32" t="s">
         <v>432</v>
       </c>
-      <c r="B34" s="35">
+      <c r="B34" s="37">
         <v>1.43</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="37">
         <v>1.03</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="37">
         <v>0.64</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="37">
         <v>4.74</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="37">
         <v>5.81</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="37">
         <v>7.04</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="37">
         <v>10.54</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="37">
         <v>11.87</v>
       </c>
-      <c r="J34" s="35">
+      <c r="J34" s="37">
         <v>1.64</v>
       </c>
-      <c r="K34" s="35">
+      <c r="K34" s="37">
         <v>1.55</v>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="37">
         <v>1.69</v>
       </c>
-      <c r="M34" s="35">
+      <c r="M34" s="37">
         <v>0.38</v>
       </c>
-      <c r="N34" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="O34" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="P34" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="Q34" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="R34" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="S34" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="T34" s="35"/>
-      <c r="U34" s="35"/>
-      <c r="V34" s="35"/>
-      <c r="W34" s="35"/>
-      <c r="X34" s="35"/>
+      <c r="N34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="P34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="Q34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="R34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="S34" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="T34" s="37"/>
+      <c r="U34" s="37"/>
+      <c r="V34" s="37"/>
+      <c r="W34" s="37"/>
+      <c r="X34" s="37"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="32" t="s">
         <v>433</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="37">
         <v>2.86</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="37">
         <v>2.02</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="37">
         <v>1.45</v>
       </c>
-      <c r="E35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="F35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="G35" s="35">
+      <c r="E35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="F35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="G35" s="37">
         <v>0.75</v>
       </c>
-      <c r="H35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="I35" s="35">
+      <c r="H35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="I35" s="37">
         <v>83.74</v>
       </c>
-      <c r="J35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="K35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="L35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="M35" s="35">
+      <c r="J35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="K35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="L35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="M35" s="37">
         <v>10.54</v>
       </c>
-      <c r="N35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="O35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="P35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="Q35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="R35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="S35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="T35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="U35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="V35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="W35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="X35" s="35"/>
+      <c r="N35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="P35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="Q35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="R35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="S35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="T35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="U35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="V35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="W35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="X35" s="37"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="32" t="s">
         <v>434</v>
       </c>
-      <c r="B36" s="35">
+      <c r="B36" s="37">
         <v>1.43</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="37">
         <v>1.03</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="37">
         <v>0.64</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="37">
         <v>6.07</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="37">
         <v>7.46</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="37">
         <v>9.03</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="37">
         <v>13.68</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="37">
         <v>15.54</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="37">
         <v>2.25</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="37">
         <v>2.12</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="37">
         <v>2.32</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="37">
         <v>0.52</v>
       </c>
-      <c r="N36" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="O36" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="P36" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="Q36" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="R36" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="S36" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="T36" s="35"/>
-      <c r="U36" s="35"/>
-      <c r="V36" s="35"/>
-      <c r="W36" s="35"/>
-      <c r="X36" s="35"/>
+      <c r="N36" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="P36" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="Q36" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="R36" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="S36" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="T36" s="37"/>
+      <c r="U36" s="37"/>
+      <c r="V36" s="37"/>
+      <c r="W36" s="37"/>
+      <c r="X36" s="37"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="31"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="32" t="s">
         <v>436</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="34">
         <v>3.32</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="34">
         <v>4.44</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="34">
         <v>3.14</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="34">
         <v>2.87</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="34">
         <v>4.86</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="34">
         <v>9.5</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="34">
         <v>2.68</v>
       </c>
-      <c r="I38" s="32">
+      <c r="I38" s="34">
         <v>1.67</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="34">
         <v>2.36</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="34">
         <v>2.43</v>
       </c>
-      <c r="L38" s="32">
+      <c r="L38" s="34">
         <v>1.36</v>
       </c>
-      <c r="M38" s="32">
+      <c r="M38" s="34">
         <v>0.78</v>
       </c>
-      <c r="N38" s="32">
+      <c r="N38" s="34">
         <v>1.0</v>
       </c>
-      <c r="O38" s="32">
+      <c r="O38" s="34">
         <v>1.18</v>
       </c>
-      <c r="P38" s="32">
+      <c r="P38" s="34">
         <v>0.34</v>
       </c>
-      <c r="Q38" s="32">
+      <c r="Q38" s="34">
         <v>0.41</v>
       </c>
-      <c r="R38" s="32">
+      <c r="R38" s="34">
         <v>0.54</v>
       </c>
-      <c r="S38" s="32">
+      <c r="S38" s="34">
         <v>0.16</v>
       </c>
-      <c r="T38" s="32">
+      <c r="T38" s="34">
         <v>2.54</v>
       </c>
-      <c r="U38" s="32">
+      <c r="U38" s="34">
         <v>1.19</v>
       </c>
-      <c r="V38" s="32">
+      <c r="V38" s="34">
         <v>1.82</v>
       </c>
-      <c r="W38" s="32">
+      <c r="W38" s="34">
         <v>1.74</v>
       </c>
-      <c r="X38" s="33"/>
+      <c r="X38" s="35"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="32" t="s">
         <v>437</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="34">
         <v>3.58</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="34">
         <v>4.16</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="34">
         <v>3.94</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="34">
         <v>3.98</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="34">
         <v>4.24</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="34">
         <v>3.69</v>
       </c>
-      <c r="H39" s="32">
+      <c r="H39" s="34">
         <v>1.97</v>
       </c>
-      <c r="I39" s="32">
+      <c r="I39" s="34">
         <v>1.38</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="34">
         <v>1.23</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="34">
         <v>1.14</v>
       </c>
-      <c r="L39" s="32">
+      <c r="L39" s="34">
         <v>0.87</v>
       </c>
-      <c r="M39" s="32">
+      <c r="M39" s="34">
         <v>0.45</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N39" s="34">
         <v>0.49</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O39" s="34">
         <v>0.31</v>
       </c>
-      <c r="P39" s="32">
+      <c r="P39" s="34">
         <v>0.93</v>
       </c>
-      <c r="Q39" s="32">
+      <c r="Q39" s="34">
         <v>0.99</v>
       </c>
-      <c r="R39" s="32">
+      <c r="R39" s="34">
         <v>1.15</v>
       </c>
-      <c r="S39" s="32">
+      <c r="S39" s="34">
         <v>1.27</v>
       </c>
-      <c r="T39" s="33"/>
-      <c r="U39" s="33"/>
-      <c r="V39" s="33"/>
-      <c r="W39" s="33"/>
-      <c r="X39" s="33"/>
+      <c r="T39" s="35"/>
+      <c r="U39" s="35"/>
+      <c r="V39" s="35"/>
+      <c r="W39" s="35"/>
+      <c r="X39" s="35"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="30" t="s">
         <v>438</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="32" t="s">
         <v>439</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="34">
         <v>5.53</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="34">
         <v>7.29</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="34">
         <v>4.29</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="34">
         <v>6.12</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="34">
         <v>4.92</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="34">
         <v>9.5</v>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="34">
         <v>2.68</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="34">
         <v>1.67</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="34">
         <v>2.42</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="34">
         <v>2.5</v>
       </c>
-      <c r="L41" s="32">
+      <c r="L41" s="34">
         <v>1.41</v>
       </c>
-      <c r="M41" s="32">
+      <c r="M41" s="34">
         <v>0.84</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N41" s="34">
         <v>1.12</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O41" s="34">
         <v>1.37</v>
       </c>
-      <c r="P41" s="32">
+      <c r="P41" s="34">
         <v>0.38</v>
       </c>
-      <c r="Q41" s="32">
+      <c r="Q41" s="34">
         <v>21.71</v>
       </c>
-      <c r="R41" s="32">
+      <c r="R41" s="34">
         <v>28.28</v>
       </c>
-      <c r="S41" s="32">
+      <c r="S41" s="34">
         <v>8.64</v>
       </c>
-      <c r="T41" s="32">
+      <c r="T41" s="34">
         <v>2.62</v>
       </c>
-      <c r="U41" s="32">
+      <c r="U41" s="34">
         <v>1.23</v>
       </c>
-      <c r="V41" s="32">
+      <c r="V41" s="34">
         <v>2.03</v>
       </c>
-      <c r="W41" s="32">
+      <c r="W41" s="34">
         <v>1.75</v>
       </c>
-      <c r="X41" s="33"/>
+      <c r="X41" s="35"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="32" t="s">
         <v>440</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="34">
         <v>5.48</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="34">
         <v>5.98</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="34">
         <v>5.25</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="34">
         <v>4.97</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="34">
         <v>4.27</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="34">
         <v>3.73</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="34">
         <v>2.0</v>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="34">
         <v>1.44</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="34">
         <v>1.31</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="34">
         <v>1.24</v>
       </c>
-      <c r="L42" s="32">
+      <c r="L42" s="34">
         <v>0.95</v>
       </c>
-      <c r="M42" s="32">
+      <c r="M42" s="34">
         <v>4.13</v>
       </c>
-      <c r="N42" s="32">
+      <c r="N42" s="34">
         <v>9.76</v>
       </c>
-      <c r="O42" s="32">
+      <c r="O42" s="34">
         <v>11.06</v>
       </c>
-      <c r="P42" s="32">
+      <c r="P42" s="34">
         <v>3.22</v>
       </c>
-      <c r="Q42" s="32">
+      <c r="Q42" s="34">
         <v>2.33</v>
       </c>
-      <c r="R42" s="32">
+      <c r="R42" s="34">
         <v>2.19</v>
       </c>
-      <c r="S42" s="32">
+      <c r="S42" s="34">
         <v>2.04</v>
       </c>
-      <c r="T42" s="33"/>
-      <c r="U42" s="33"/>
-      <c r="V42" s="33"/>
-      <c r="W42" s="33"/>
-      <c r="X42" s="33"/>
+      <c r="T42" s="35"/>
+      <c r="U42" s="35"/>
+      <c r="V42" s="35"/>
+      <c r="W42" s="35"/>
+      <c r="X42" s="35"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="30" t="s">
         <v>441</v>
       </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="31"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
+      <c r="A44" s="32" t="s">
         <v>442</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="34">
         <v>13.45</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="33">
         <v>805.02</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="33">
         <v>142.93</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="34">
         <v>10.73</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="34">
         <v>54.61</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="34">
         <v>39.57</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="34">
         <v>6.8</v>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="34">
         <v>5.35</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="34">
         <v>8.0</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="34">
         <v>4.35</v>
       </c>
-      <c r="L44" s="32">
+      <c r="L44" s="34">
         <v>2.27</v>
       </c>
-      <c r="M44" s="32">
+      <c r="M44" s="34">
         <v>0.93</v>
       </c>
-      <c r="N44" s="32">
+      <c r="N44" s="34">
         <v>1.24</v>
       </c>
-      <c r="O44" s="32">
+      <c r="O44" s="34">
         <v>0.98</v>
       </c>
-      <c r="P44" s="32">
+      <c r="P44" s="34">
         <v>0.08</v>
       </c>
-      <c r="Q44" s="32">
+      <c r="Q44" s="34">
         <v>4.49</v>
       </c>
-      <c r="R44" s="32">
+      <c r="R44" s="34">
         <v>2.15</v>
       </c>
-      <c r="S44" s="32">
+      <c r="S44" s="34">
         <v>1.08</v>
       </c>
-      <c r="T44" s="32">
+      <c r="T44" s="34">
         <v>14.25</v>
       </c>
-      <c r="U44" s="33">
+      <c r="U44" s="35">
         <v>35388.43</v>
       </c>
-      <c r="V44" s="32">
+      <c r="V44" s="34">
         <v>8.8</v>
       </c>
-      <c r="W44" s="31">
+      <c r="W44" s="33">
         <v>252.86</v>
       </c>
-      <c r="X44" s="33"/>
+      <c r="X44" s="35"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="32" t="s">
         <v>443</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="34">
         <v>29.95</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="34">
         <v>41.36</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="34">
         <v>25.2</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="34">
         <v>15.77</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="34">
         <v>16.73</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="34">
         <v>10.2</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="34">
         <v>4.28</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="34">
         <v>2.18</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="34">
         <v>1.7</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="34">
         <v>1.35</v>
       </c>
-      <c r="L45" s="32">
+      <c r="L45" s="34">
         <v>0.52</v>
       </c>
-      <c r="M45" s="32">
+      <c r="M45" s="34">
         <v>1.69</v>
       </c>
-      <c r="N45" s="32">
+      <c r="N45" s="34">
         <v>1.97</v>
       </c>
-      <c r="O45" s="32">
+      <c r="O45" s="34">
         <v>1.61</v>
       </c>
-      <c r="P45" s="32">
+      <c r="P45" s="34">
         <v>5.05</v>
       </c>
-      <c r="Q45" s="32">
+      <c r="Q45" s="34">
         <v>7.39</v>
       </c>
-      <c r="R45" s="32">
+      <c r="R45" s="34">
         <v>7.83</v>
       </c>
-      <c r="S45" s="32">
+      <c r="S45" s="34">
         <v>10.14</v>
       </c>
-      <c r="T45" s="33"/>
-      <c r="U45" s="33"/>
-      <c r="V45" s="33"/>
-      <c r="W45" s="33"/>
-      <c r="X45" s="33"/>
+      <c r="T45" s="35"/>
+      <c r="U45" s="35"/>
+      <c r="V45" s="35"/>
+      <c r="W45" s="35"/>
+      <c r="X45" s="35"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
+      <c r="A46" s="30" t="s">
         <v>444</v>
       </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
+      <c r="S46" s="31"/>
+      <c r="T46" s="31"/>
+      <c r="U46" s="31"/>
+      <c r="V46" s="31"/>
+      <c r="W46" s="31"/>
+      <c r="X46" s="31"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="32" t="s">
         <v>445</v>
       </c>
-      <c r="B47" s="33"/>
-      <c r="C47" s="33"/>
-      <c r="D47" s="32">
+      <c r="B47" s="35"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="34">
         <v>80.07</v>
       </c>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="32">
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="34">
         <v>37.58</v>
       </c>
-      <c r="H47" s="32">
+      <c r="H47" s="34">
         <v>11.09</v>
       </c>
-      <c r="I47" s="32">
+      <c r="I47" s="34">
         <v>8.58</v>
       </c>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="33"/>
-      <c r="M47" s="33"/>
-      <c r="N47" s="32">
+      <c r="J47" s="35"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="35"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="34">
         <v>53.08</v>
       </c>
-      <c r="O47" s="32">
+      <c r="O47" s="34">
         <v>2.57</v>
       </c>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="33"/>
-      <c r="S47" s="33"/>
-      <c r="T47" s="33"/>
-      <c r="U47" s="33"/>
-      <c r="V47" s="33"/>
-      <c r="W47" s="33"/>
-      <c r="X47" s="33"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="35"/>
+      <c r="R47" s="35"/>
+      <c r="S47" s="35"/>
+      <c r="T47" s="35"/>
+      <c r="U47" s="35"/>
+      <c r="V47" s="35"/>
+      <c r="W47" s="35"/>
+      <c r="X47" s="35"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="32" t="s">
         <v>446</v>
       </c>
-      <c r="B48" s="33"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="31">
+      <c r="B48" s="35"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="33">
         <v>245.77</v>
       </c>
-      <c r="F48" s="32">
+      <c r="F48" s="34">
         <v>54.36</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="34">
         <v>87.46</v>
       </c>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="32">
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="34">
         <v>60.03</v>
       </c>
-      <c r="L48" s="33"/>
-      <c r="M48" s="33"/>
-      <c r="N48" s="33"/>
-      <c r="O48" s="33"/>
-      <c r="P48" s="33"/>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33"/>
-      <c r="S48" s="33"/>
-      <c r="T48" s="33"/>
-      <c r="U48" s="33"/>
-      <c r="V48" s="33"/>
-      <c r="W48" s="33"/>
-      <c r="X48" s="33"/>
+      <c r="L48" s="35"/>
+      <c r="M48" s="35"/>
+      <c r="N48" s="35"/>
+      <c r="O48" s="35"/>
+      <c r="P48" s="35"/>
+      <c r="Q48" s="35"/>
+      <c r="R48" s="35"/>
+      <c r="S48" s="35"/>
+      <c r="T48" s="35"/>
+      <c r="U48" s="35"/>
+      <c r="V48" s="35"/>
+      <c r="W48" s="35"/>
+      <c r="X48" s="35"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
+      <c r="S49" s="31"/>
+      <c r="T49" s="31"/>
+      <c r="U49" s="31"/>
+      <c r="V49" s="31"/>
+      <c r="W49" s="31"/>
+      <c r="X49" s="31"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="32" t="s">
         <v>448</v>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="33">
         <v>119.5</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="34">
         <v>6.99</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="34">
         <v>9.85</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="33">
         <v>127.79</v>
       </c>
-      <c r="F50" s="33"/>
-      <c r="G50" s="33"/>
-      <c r="H50" s="32">
+      <c r="F50" s="35"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="34">
         <v>13.28</v>
       </c>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="33"/>
-      <c r="M50" s="33"/>
-      <c r="N50" s="32">
+      <c r="I50" s="35"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="34">
         <v>3.93</v>
       </c>
-      <c r="O50" s="32">
+      <c r="O50" s="34">
         <v>2.72</v>
       </c>
-      <c r="P50" s="33"/>
-      <c r="Q50" s="32">
+      <c r="P50" s="35"/>
+      <c r="Q50" s="34">
         <v>4.35</v>
       </c>
-      <c r="R50" s="33"/>
-      <c r="S50" s="33"/>
-      <c r="T50" s="33"/>
-      <c r="U50" s="33"/>
-      <c r="V50" s="33"/>
-      <c r="W50" s="33"/>
-      <c r="X50" s="33"/>
+      <c r="R50" s="35"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="35"/>
+      <c r="U50" s="35"/>
+      <c r="V50" s="35"/>
+      <c r="W50" s="35"/>
+      <c r="X50" s="35"/>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="28" t="s">
+      <c r="A51" s="30" t="s">
         <v>449</v>
       </c>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
-      <c r="F51" s="29"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="29"/>
-      <c r="I51" s="29"/>
-      <c r="J51" s="29"/>
-      <c r="K51" s="29"/>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29"/>
-      <c r="N51" s="29"/>
-      <c r="O51" s="29"/>
-      <c r="P51" s="29"/>
-      <c r="Q51" s="29"/>
-      <c r="R51" s="29"/>
-      <c r="S51" s="29"/>
-      <c r="T51" s="29"/>
-      <c r="U51" s="29"/>
-      <c r="V51" s="29"/>
-      <c r="W51" s="29"/>
-      <c r="X51" s="29"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="31"/>
+      <c r="D51" s="31"/>
+      <c r="E51" s="31"/>
+      <c r="F51" s="31"/>
+      <c r="G51" s="31"/>
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="31"/>
+      <c r="M51" s="31"/>
+      <c r="N51" s="31"/>
+      <c r="O51" s="31"/>
+      <c r="P51" s="31"/>
+      <c r="Q51" s="31"/>
+      <c r="R51" s="31"/>
+      <c r="S51" s="31"/>
+      <c r="T51" s="31"/>
+      <c r="U51" s="31"/>
+      <c r="V51" s="31"/>
+      <c r="W51" s="31"/>
+      <c r="X51" s="31"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="30" t="s">
+      <c r="A52" s="32" t="s">
         <v>450</v>
       </c>
-      <c r="B52" s="32">
+      <c r="B52" s="34">
         <v>65.4</v>
       </c>
-      <c r="C52" s="32">
+      <c r="C52" s="34">
         <v>6.66</v>
       </c>
-      <c r="D52" s="32">
+      <c r="D52" s="34">
         <v>9.19</v>
       </c>
-      <c r="E52" s="32">
+      <c r="E52" s="34">
         <v>78.72</v>
       </c>
-      <c r="F52" s="33"/>
-      <c r="G52" s="32">
+      <c r="F52" s="35"/>
+      <c r="G52" s="34">
         <v>39.43</v>
       </c>
-      <c r="H52" s="32">
+      <c r="H52" s="34">
         <v>14.0</v>
       </c>
-      <c r="I52" s="32">
+      <c r="I52" s="34">
         <v>4.32</v>
       </c>
-      <c r="J52" s="33"/>
-      <c r="K52" s="33"/>
-      <c r="L52" s="33"/>
-      <c r="M52" s="33"/>
-      <c r="N52" s="32">
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
+      <c r="M52" s="35"/>
+      <c r="N52" s="34">
         <v>4.18</v>
       </c>
-      <c r="O52" s="33"/>
-      <c r="P52" s="33"/>
-      <c r="Q52" s="33"/>
-      <c r="R52" s="33"/>
-      <c r="S52" s="33"/>
-      <c r="T52" s="33"/>
-      <c r="U52" s="33"/>
-      <c r="V52" s="33"/>
-      <c r="W52" s="33"/>
-      <c r="X52" s="33"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="35"/>
+      <c r="R52" s="35"/>
+      <c r="S52" s="35"/>
+      <c r="T52" s="35"/>
+      <c r="U52" s="35"/>
+      <c r="V52" s="35"/>
+      <c r="W52" s="35"/>
+      <c r="X52" s="35"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="32" t="s">
         <v>451</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="34">
         <v>16.38</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="34">
         <v>16.04</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="34">
         <v>29.59</v>
       </c>
-      <c r="E53" s="32">
+      <c r="E53" s="34">
         <v>60.51</v>
       </c>
-      <c r="F53" s="31">
+      <c r="F53" s="33">
         <v>117.62</v>
       </c>
-      <c r="G53" s="33"/>
-      <c r="H53" s="33"/>
-      <c r="I53" s="33"/>
-      <c r="J53" s="33"/>
-      <c r="K53" s="33"/>
-      <c r="L53" s="33"/>
-      <c r="M53" s="33"/>
-      <c r="N53" s="33"/>
-      <c r="O53" s="33"/>
-      <c r="P53" s="33"/>
-      <c r="Q53" s="33"/>
-      <c r="R53" s="33"/>
-      <c r="S53" s="33"/>
-      <c r="T53" s="33"/>
-      <c r="U53" s="33"/>
-      <c r="V53" s="33"/>
-      <c r="W53" s="33"/>
-      <c r="X53" s="33"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="35"/>
+      <c r="I53" s="35"/>
+      <c r="J53" s="35"/>
+      <c r="K53" s="35"/>
+      <c r="L53" s="35"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
+      <c r="Q53" s="35"/>
+      <c r="R53" s="35"/>
+      <c r="S53" s="35"/>
+      <c r="T53" s="35"/>
+      <c r="U53" s="35"/>
+      <c r="V53" s="35"/>
+      <c r="W53" s="35"/>
+      <c r="X53" s="35"/>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="28" t="s">
+      <c r="A54" s="30" t="s">
         <v>452</v>
       </c>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="29"/>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29"/>
-      <c r="L54" s="29"/>
-      <c r="M54" s="29"/>
-      <c r="N54" s="29"/>
-      <c r="O54" s="29"/>
-      <c r="P54" s="29"/>
-      <c r="Q54" s="29"/>
-      <c r="R54" s="29"/>
-      <c r="S54" s="29"/>
-      <c r="T54" s="29"/>
-      <c r="U54" s="29"/>
-      <c r="V54" s="29"/>
-      <c r="W54" s="29"/>
-      <c r="X54" s="29"/>
+      <c r="B54" s="31"/>
+      <c r="C54" s="31"/>
+      <c r="D54" s="31"/>
+      <c r="E54" s="31"/>
+      <c r="F54" s="31"/>
+      <c r="G54" s="31"/>
+      <c r="H54" s="31"/>
+      <c r="I54" s="31"/>
+      <c r="J54" s="31"/>
+      <c r="K54" s="31"/>
+      <c r="L54" s="31"/>
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="31"/>
+      <c r="P54" s="31"/>
+      <c r="Q54" s="31"/>
+      <c r="R54" s="31"/>
+      <c r="S54" s="31"/>
+      <c r="T54" s="31"/>
+      <c r="U54" s="31"/>
+      <c r="V54" s="31"/>
+      <c r="W54" s="31"/>
+      <c r="X54" s="31"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="30" t="s">
+      <c r="A55" s="32" t="s">
         <v>453</v>
       </c>
-      <c r="B55" s="31">
+      <c r="B55" s="33">
         <v>187.79</v>
       </c>
-      <c r="C55" s="33"/>
-      <c r="D55" s="33"/>
-      <c r="E55" s="32">
+      <c r="C55" s="35"/>
+      <c r="D55" s="35"/>
+      <c r="E55" s="34">
         <v>16.1</v>
       </c>
-      <c r="F55" s="33"/>
-      <c r="G55" s="32">
+      <c r="F55" s="35"/>
+      <c r="G55" s="34">
         <v>39.43</v>
       </c>
-      <c r="H55" s="32">
+      <c r="H55" s="34">
         <v>14.0</v>
       </c>
-      <c r="I55" s="32">
+      <c r="I55" s="34">
         <v>4.32</v>
       </c>
-      <c r="J55" s="33"/>
-      <c r="K55" s="33"/>
-      <c r="L55" s="33"/>
-      <c r="M55" s="31">
+      <c r="J55" s="35"/>
+      <c r="K55" s="35"/>
+      <c r="L55" s="35"/>
+      <c r="M55" s="33">
         <v>105.53</v>
       </c>
-      <c r="N55" s="32">
+      <c r="N55" s="34">
         <v>4.16</v>
       </c>
-      <c r="O55" s="33"/>
-      <c r="P55" s="33"/>
-      <c r="Q55" s="33"/>
-      <c r="R55" s="33"/>
-      <c r="S55" s="33"/>
-      <c r="T55" s="33"/>
-      <c r="U55" s="33"/>
-      <c r="V55" s="33"/>
-      <c r="W55" s="33"/>
-      <c r="X55" s="33"/>
+      <c r="O55" s="35"/>
+      <c r="P55" s="35"/>
+      <c r="Q55" s="35"/>
+      <c r="R55" s="35"/>
+      <c r="S55" s="35"/>
+      <c r="T55" s="35"/>
+      <c r="U55" s="35"/>
+      <c r="V55" s="35"/>
+      <c r="W55" s="35"/>
+      <c r="X55" s="35"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="32" t="s">
         <v>454</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="34">
         <v>3.58</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="34">
         <v>4.16</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="34">
         <v>3.94</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="34">
         <v>3.98</v>
       </c>
-      <c r="F56" s="32">
+      <c r="F56" s="34">
         <v>4.24</v>
       </c>
-      <c r="G56" s="32">
+      <c r="G56" s="34">
         <v>3.69</v>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="34">
         <v>1.97</v>
       </c>
-      <c r="I56" s="32">
+      <c r="I56" s="34">
         <v>1.38</v>
       </c>
-      <c r="J56" s="32">
+      <c r="J56" s="34">
         <v>1.23</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="34">
         <v>1.14</v>
       </c>
-      <c r="L56" s="32">
+      <c r="L56" s="34">
         <v>0.87</v>
       </c>
-      <c r="M56" s="32">
+      <c r="M56" s="34">
         <v>3.78</v>
       </c>
-      <c r="N56" s="32">
+      <c r="N56" s="34">
         <v>8.99</v>
       </c>
-      <c r="O56" s="32">
+      <c r="O56" s="34">
         <v>10.4</v>
       </c>
-      <c r="P56" s="32">
+      <c r="P56" s="34">
         <v>3.11</v>
       </c>
-      <c r="Q56" s="32">
+      <c r="Q56" s="34">
         <v>2.26</v>
       </c>
-      <c r="R56" s="32">
+      <c r="R56" s="34">
         <v>2.09</v>
       </c>
-      <c r="S56" s="32">
+      <c r="S56" s="34">
         <v>1.95</v>
       </c>
-      <c r="T56" s="33"/>
-      <c r="U56" s="33"/>
-      <c r="V56" s="33"/>
-      <c r="W56" s="33"/>
-      <c r="X56" s="33"/>
+      <c r="T56" s="35"/>
+      <c r="U56" s="35"/>
+      <c r="V56" s="35"/>
+      <c r="W56" s="35"/>
+      <c r="X56" s="35"/>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="28" t="s">
+      <c r="A57" s="30" t="s">
         <v>455</v>
       </c>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
-      <c r="F57" s="29"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29"/>
-      <c r="I57" s="29"/>
-      <c r="J57" s="29"/>
-      <c r="K57" s="29"/>
-      <c r="L57" s="29"/>
-      <c r="M57" s="29"/>
-      <c r="N57" s="29"/>
-      <c r="O57" s="29"/>
-      <c r="P57" s="29"/>
-      <c r="Q57" s="29"/>
-      <c r="R57" s="29"/>
-      <c r="S57" s="29"/>
-      <c r="T57" s="29"/>
-      <c r="U57" s="29"/>
-      <c r="V57" s="29"/>
-      <c r="W57" s="29"/>
-      <c r="X57" s="29"/>
+      <c r="B57" s="31"/>
+      <c r="C57" s="31"/>
+      <c r="D57" s="31"/>
+      <c r="E57" s="31"/>
+      <c r="F57" s="31"/>
+      <c r="G57" s="31"/>
+      <c r="H57" s="31"/>
+      <c r="I57" s="31"/>
+      <c r="J57" s="31"/>
+      <c r="K57" s="31"/>
+      <c r="L57" s="31"/>
+      <c r="M57" s="31"/>
+      <c r="N57" s="31"/>
+      <c r="O57" s="31"/>
+      <c r="P57" s="31"/>
+      <c r="Q57" s="31"/>
+      <c r="R57" s="31"/>
+      <c r="S57" s="31"/>
+      <c r="T57" s="31"/>
+      <c r="U57" s="31"/>
+      <c r="V57" s="31"/>
+      <c r="W57" s="31"/>
+      <c r="X57" s="31"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="30" t="s">
+      <c r="A58" s="32" t="s">
         <v>456</v>
       </c>
-      <c r="B58" s="36">
+      <c r="B58" s="38">
         <v>-0.7</v>
       </c>
-      <c r="C58" s="32">
+      <c r="C58" s="34">
         <v>0.14</v>
       </c>
-      <c r="D58" s="32">
+      <c r="D58" s="34">
         <v>0.01</v>
       </c>
-      <c r="E58" s="32">
+      <c r="E58" s="34">
         <v>0.66</v>
       </c>
-      <c r="F58" s="33"/>
-      <c r="G58" s="32">
+      <c r="F58" s="35"/>
+      <c r="G58" s="34">
         <v>0.96</v>
       </c>
-      <c r="H58" s="36">
+      <c r="H58" s="38">
         <v>-0.23</v>
       </c>
-      <c r="I58" s="32">
+      <c r="I58" s="34">
         <v>0.01</v>
       </c>
-      <c r="J58" s="33"/>
-      <c r="K58" s="33"/>
-      <c r="L58" s="33"/>
-      <c r="M58" s="33"/>
-      <c r="N58" s="32">
+      <c r="J58" s="35"/>
+      <c r="K58" s="35"/>
+      <c r="L58" s="35"/>
+      <c r="M58" s="35"/>
+      <c r="N58" s="34">
         <v>0.01</v>
       </c>
-      <c r="O58" s="33"/>
-      <c r="P58" s="33"/>
-      <c r="Q58" s="33"/>
-      <c r="R58" s="33"/>
-      <c r="S58" s="33"/>
-      <c r="T58" s="33"/>
-      <c r="U58" s="33"/>
-      <c r="V58" s="33"/>
-      <c r="W58" s="33"/>
-      <c r="X58" s="33"/>
+      <c r="O58" s="35"/>
+      <c r="P58" s="35"/>
+      <c r="Q58" s="35"/>
+      <c r="R58" s="35"/>
+      <c r="S58" s="35"/>
+      <c r="T58" s="35"/>
+      <c r="U58" s="35"/>
+      <c r="V58" s="35"/>
+      <c r="W58" s="35"/>
+      <c r="X58" s="35"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
+      <c r="A59" s="32" t="s">
         <v>457</v>
       </c>
-      <c r="B59" s="36">
+      <c r="B59" s="38">
         <v>-1.47</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="34">
         <v>0.26</v>
       </c>
-      <c r="D59" s="32">
+      <c r="D59" s="34">
         <v>1.3</v>
       </c>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="33"/>
-      <c r="H59" s="33"/>
-      <c r="I59" s="33"/>
-      <c r="J59" s="33"/>
-      <c r="K59" s="33"/>
-      <c r="L59" s="33"/>
-      <c r="M59" s="33"/>
-      <c r="N59" s="33"/>
-      <c r="O59" s="33"/>
-      <c r="P59" s="33"/>
-      <c r="Q59" s="33"/>
-      <c r="R59" s="33"/>
-      <c r="S59" s="33"/>
-      <c r="T59" s="33"/>
-      <c r="U59" s="33"/>
-      <c r="V59" s="33"/>
-      <c r="W59" s="33"/>
-      <c r="X59" s="33"/>
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="35"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="35"/>
+      <c r="M59" s="35"/>
+      <c r="N59" s="35"/>
+      <c r="O59" s="35"/>
+      <c r="P59" s="35"/>
+      <c r="Q59" s="35"/>
+      <c r="R59" s="35"/>
+      <c r="S59" s="35"/>
+      <c r="T59" s="35"/>
+      <c r="U59" s="35"/>
+      <c r="V59" s="35"/>
+      <c r="W59" s="35"/>
+      <c r="X59" s="35"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="28" t="s">
+      <c r="A60" s="30" t="s">
         <v>458</v>
       </c>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
-      <c r="F60" s="29"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="29"/>
-      <c r="I60" s="29"/>
-      <c r="J60" s="29"/>
-      <c r="K60" s="29"/>
-      <c r="L60" s="29"/>
-      <c r="M60" s="29"/>
-      <c r="N60" s="29"/>
-      <c r="O60" s="29"/>
-      <c r="P60" s="29"/>
-      <c r="Q60" s="29"/>
-      <c r="R60" s="29"/>
-      <c r="S60" s="29"/>
-      <c r="T60" s="29"/>
-      <c r="U60" s="29"/>
-      <c r="V60" s="29"/>
-      <c r="W60" s="29"/>
-      <c r="X60" s="29"/>
+      <c r="B60" s="31"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="31"/>
+      <c r="F60" s="31"/>
+      <c r="G60" s="31"/>
+      <c r="H60" s="31"/>
+      <c r="I60" s="31"/>
+      <c r="J60" s="31"/>
+      <c r="K60" s="31"/>
+      <c r="L60" s="31"/>
+      <c r="M60" s="31"/>
+      <c r="N60" s="31"/>
+      <c r="O60" s="31"/>
+      <c r="P60" s="31"/>
+      <c r="Q60" s="31"/>
+      <c r="R60" s="31"/>
+      <c r="S60" s="31"/>
+      <c r="T60" s="31"/>
+      <c r="U60" s="31"/>
+      <c r="V60" s="31"/>
+      <c r="W60" s="31"/>
+      <c r="X60" s="31"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="30" t="s">
+      <c r="A61" s="32" t="s">
         <v>459</v>
       </c>
-      <c r="B61" s="32">
+      <c r="B61" s="34">
         <v>11.38</v>
       </c>
-      <c r="C61" s="31">
+      <c r="C61" s="33">
         <v>676.24</v>
       </c>
-      <c r="D61" s="31">
+      <c r="D61" s="33">
         <v>113.16</v>
       </c>
-      <c r="E61" s="32">
+      <c r="E61" s="34">
         <v>11.27</v>
       </c>
-      <c r="F61" s="32">
+      <c r="F61" s="34">
         <v>48.63</v>
       </c>
-      <c r="G61" s="32">
+      <c r="G61" s="34">
         <v>37.3</v>
       </c>
-      <c r="H61" s="32">
+      <c r="H61" s="34">
         <v>5.1</v>
       </c>
-      <c r="I61" s="32">
+      <c r="I61" s="34">
         <v>1.81</v>
       </c>
-      <c r="J61" s="32">
+      <c r="J61" s="34">
         <v>4.36</v>
       </c>
-      <c r="K61" s="32">
+      <c r="K61" s="34">
         <v>2.6</v>
       </c>
-      <c r="L61" s="32">
+      <c r="L61" s="34">
         <v>1.14</v>
       </c>
-      <c r="M61" s="32">
+      <c r="M61" s="34">
         <v>0.71</v>
       </c>
-      <c r="N61" s="32">
+      <c r="N61" s="34">
         <v>0.86</v>
       </c>
-      <c r="O61" s="32">
+      <c r="O61" s="34">
         <v>0.45</v>
       </c>
-      <c r="P61" s="32">
+      <c r="P61" s="34">
         <v>0.04</v>
       </c>
-      <c r="Q61" s="32">
+      <c r="Q61" s="34">
         <v>22.19</v>
       </c>
-      <c r="R61" s="32">
+      <c r="R61" s="34">
         <v>12.77</v>
       </c>
-      <c r="S61" s="32">
+      <c r="S61" s="34">
         <v>10.94</v>
       </c>
-      <c r="T61" s="32">
+      <c r="T61" s="34">
         <v>23.67</v>
       </c>
-      <c r="U61" s="32">
+      <c r="U61" s="34">
         <v>24.6</v>
       </c>
-      <c r="V61" s="32">
+      <c r="V61" s="34">
         <v>12.71</v>
       </c>
-      <c r="W61" s="31">
+      <c r="W61" s="33">
         <v>286.56</v>
       </c>
-      <c r="X61" s="33"/>
+      <c r="X61" s="35"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
+      <c r="A62" s="32" t="s">
         <v>460</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="34">
         <v>26.52</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="34">
         <v>38.45</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="34">
         <v>23.35</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="34">
         <v>12.82</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="34">
         <v>11.31</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="34">
         <v>6.22</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="34">
         <v>2.23</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="34">
         <v>1.24</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62" s="34">
         <v>1.08</v>
       </c>
-      <c r="K62" s="32">
+      <c r="K62" s="34">
         <v>0.82</v>
       </c>
-      <c r="L62" s="32">
+      <c r="L62" s="34">
         <v>0.58</v>
       </c>
-      <c r="M62" s="32">
+      <c r="M62" s="34">
         <v>3.81</v>
       </c>
-      <c r="N62" s="32">
+      <c r="N62" s="34">
         <v>7.59</v>
       </c>
-      <c r="O62" s="32">
+      <c r="O62" s="34">
         <v>9.39</v>
       </c>
-      <c r="P62" s="32">
+      <c r="P62" s="34">
         <v>13.05</v>
       </c>
-      <c r="Q62" s="32">
+      <c r="Q62" s="34">
         <v>16.06</v>
       </c>
-      <c r="R62" s="32">
+      <c r="R62" s="34">
         <v>14.88</v>
       </c>
-      <c r="S62" s="32">
+      <c r="S62" s="34">
         <v>16.85</v>
       </c>
-      <c r="T62" s="33"/>
-      <c r="U62" s="33"/>
-      <c r="V62" s="33"/>
-      <c r="W62" s="33"/>
-      <c r="X62" s="33"/>
+      <c r="T62" s="35"/>
+      <c r="U62" s="35"/>
+      <c r="V62" s="35"/>
+      <c r="W62" s="35"/>
+      <c r="X62" s="35"/>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="28" t="s">
+      <c r="A63" s="30" t="s">
         <v>461</v>
       </c>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
-      <c r="F63" s="29"/>
-      <c r="G63" s="29"/>
-      <c r="H63" s="29"/>
-      <c r="I63" s="29"/>
-      <c r="J63" s="29"/>
-      <c r="K63" s="29"/>
-      <c r="L63" s="29"/>
-      <c r="M63" s="29"/>
-      <c r="N63" s="29"/>
-      <c r="O63" s="29"/>
-      <c r="P63" s="29"/>
-      <c r="Q63" s="29"/>
-      <c r="R63" s="29"/>
-      <c r="S63" s="29"/>
-      <c r="T63" s="29"/>
-      <c r="U63" s="29"/>
-      <c r="V63" s="29"/>
-      <c r="W63" s="29"/>
-      <c r="X63" s="29"/>
+      <c r="B63" s="31"/>
+      <c r="C63" s="31"/>
+      <c r="D63" s="31"/>
+      <c r="E63" s="31"/>
+      <c r="F63" s="31"/>
+      <c r="G63" s="31"/>
+      <c r="H63" s="31"/>
+      <c r="I63" s="31"/>
+      <c r="J63" s="31"/>
+      <c r="K63" s="31"/>
+      <c r="L63" s="31"/>
+      <c r="M63" s="31"/>
+      <c r="N63" s="31"/>
+      <c r="O63" s="31"/>
+      <c r="P63" s="31"/>
+      <c r="Q63" s="31"/>
+      <c r="R63" s="31"/>
+      <c r="S63" s="31"/>
+      <c r="T63" s="31"/>
+      <c r="U63" s="31"/>
+      <c r="V63" s="31"/>
+      <c r="W63" s="31"/>
+      <c r="X63" s="31"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="30" t="s">
+      <c r="A64" s="32" t="s">
         <v>462</v>
       </c>
-      <c r="B64" s="33"/>
-      <c r="C64" s="33"/>
-      <c r="D64" s="33"/>
-      <c r="E64" s="32">
+      <c r="B64" s="35"/>
+      <c r="C64" s="35"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="34">
         <v>16.2</v>
       </c>
-      <c r="F64" s="33"/>
-      <c r="G64" s="31">
+      <c r="F64" s="35"/>
+      <c r="G64" s="33">
         <v>151.34</v>
       </c>
-      <c r="H64" s="32">
+      <c r="H64" s="34">
         <v>8.31</v>
       </c>
-      <c r="I64" s="32">
+      <c r="I64" s="34">
         <v>3.02</v>
       </c>
-      <c r="J64" s="33"/>
-      <c r="K64" s="33"/>
-      <c r="L64" s="33"/>
-      <c r="M64" s="32">
+      <c r="J64" s="35"/>
+      <c r="K64" s="35"/>
+      <c r="L64" s="35"/>
+      <c r="M64" s="34">
         <v>5.73</v>
       </c>
-      <c r="N64" s="32">
+      <c r="N64" s="34">
         <v>8.16</v>
       </c>
-      <c r="O64" s="32">
+      <c r="O64" s="34">
         <v>1.77</v>
       </c>
-      <c r="P64" s="32">
+      <c r="P64" s="34">
         <v>0.79</v>
       </c>
-      <c r="Q64" s="32">
+      <c r="Q64" s="34">
         <v>14.77</v>
       </c>
-      <c r="R64" s="33"/>
-      <c r="S64" s="33"/>
-      <c r="T64" s="33"/>
-      <c r="U64" s="33"/>
-      <c r="V64" s="33"/>
-      <c r="W64" s="33"/>
-      <c r="X64" s="33"/>
+      <c r="R64" s="35"/>
+      <c r="S64" s="35"/>
+      <c r="T64" s="35"/>
+      <c r="U64" s="35"/>
+      <c r="V64" s="35"/>
+      <c r="W64" s="35"/>
+      <c r="X64" s="35"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
+      <c r="A65" s="32" t="s">
         <v>463</v>
       </c>
-      <c r="B65" s="33"/>
-      <c r="C65" s="33"/>
-      <c r="D65" s="31">
+      <c r="B65" s="35"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="33">
         <v>322.14</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="34">
         <v>25.82</v>
       </c>
-      <c r="F65" s="33"/>
-      <c r="G65" s="33"/>
-      <c r="H65" s="33"/>
-      <c r="I65" s="33"/>
-      <c r="J65" s="33"/>
-      <c r="K65" s="32">
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35"/>
+      <c r="I65" s="35"/>
+      <c r="J65" s="35"/>
+      <c r="K65" s="34">
         <v>13.97</v>
       </c>
-      <c r="L65" s="32">
+      <c r="L65" s="34">
         <v>5.79</v>
       </c>
-      <c r="M65" s="32">
+      <c r="M65" s="34">
         <v>11.1</v>
       </c>
-      <c r="N65" s="32">
+      <c r="N65" s="34">
         <v>30.5</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="33">
         <v>149.19</v>
       </c>
-      <c r="P65" s="33"/>
-      <c r="Q65" s="33"/>
-      <c r="R65" s="33"/>
-      <c r="S65" s="33"/>
-      <c r="T65" s="33"/>
-      <c r="U65" s="33"/>
-      <c r="V65" s="33"/>
-      <c r="W65" s="33"/>
-      <c r="X65" s="33"/>
+      <c r="P65" s="35"/>
+      <c r="Q65" s="35"/>
+      <c r="R65" s="35"/>
+      <c r="S65" s="35"/>
+      <c r="T65" s="35"/>
+      <c r="U65" s="35"/>
+      <c r="V65" s="35"/>
+      <c r="W65" s="35"/>
+      <c r="X65" s="35"/>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="28" t="s">
+      <c r="A66" s="30" t="s">
         <v>464</v>
       </c>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
-      <c r="F66" s="29"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="29"/>
-      <c r="I66" s="29"/>
-      <c r="J66" s="29"/>
-      <c r="K66" s="29"/>
-      <c r="L66" s="29"/>
-      <c r="M66" s="29"/>
-      <c r="N66" s="29"/>
-      <c r="O66" s="29"/>
-      <c r="P66" s="29"/>
-      <c r="Q66" s="29"/>
-      <c r="R66" s="29"/>
-      <c r="S66" s="29"/>
-      <c r="T66" s="29"/>
-      <c r="U66" s="29"/>
-      <c r="V66" s="29"/>
-      <c r="W66" s="29"/>
-      <c r="X66" s="29"/>
+      <c r="B66" s="31"/>
+      <c r="C66" s="31"/>
+      <c r="D66" s="31"/>
+      <c r="E66" s="31"/>
+      <c r="F66" s="31"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="31"/>
+      <c r="I66" s="31"/>
+      <c r="J66" s="31"/>
+      <c r="K66" s="31"/>
+      <c r="L66" s="31"/>
+      <c r="M66" s="31"/>
+      <c r="N66" s="31"/>
+      <c r="O66" s="31"/>
+      <c r="P66" s="31"/>
+      <c r="Q66" s="31"/>
+      <c r="R66" s="31"/>
+      <c r="S66" s="31"/>
+      <c r="T66" s="31"/>
+      <c r="U66" s="31"/>
+      <c r="V66" s="31"/>
+      <c r="W66" s="31"/>
+      <c r="X66" s="31"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="30" t="s">
+      <c r="A67" s="32" t="s">
         <v>465</v>
       </c>
-      <c r="B67" s="33"/>
-      <c r="C67" s="33"/>
-      <c r="D67" s="32">
+      <c r="B67" s="35"/>
+      <c r="C67" s="35"/>
+      <c r="D67" s="34">
         <v>50.53</v>
       </c>
-      <c r="E67" s="33"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="32">
+      <c r="E67" s="35"/>
+      <c r="F67" s="35"/>
+      <c r="G67" s="34">
         <v>35.43</v>
       </c>
-      <c r="H67" s="32">
+      <c r="H67" s="34">
         <v>8.31</v>
       </c>
-      <c r="I67" s="32">
+      <c r="I67" s="34">
         <v>2.9</v>
       </c>
-      <c r="J67" s="33"/>
-      <c r="K67" s="33"/>
-      <c r="L67" s="33"/>
-      <c r="M67" s="33"/>
-      <c r="N67" s="32">
+      <c r="J67" s="35"/>
+      <c r="K67" s="35"/>
+      <c r="L67" s="35"/>
+      <c r="M67" s="35"/>
+      <c r="N67" s="34">
         <v>33.9</v>
       </c>
-      <c r="O67" s="32">
+      <c r="O67" s="34">
         <v>1.13</v>
       </c>
-      <c r="P67" s="33"/>
-      <c r="Q67" s="33"/>
-      <c r="R67" s="33"/>
-      <c r="S67" s="33"/>
-      <c r="T67" s="33"/>
-      <c r="U67" s="32">
+      <c r="P67" s="35"/>
+      <c r="Q67" s="35"/>
+      <c r="R67" s="35"/>
+      <c r="S67" s="35"/>
+      <c r="T67" s="35"/>
+      <c r="U67" s="34">
         <v>15.23</v>
       </c>
-      <c r="V67" s="32">
+      <c r="V67" s="34">
         <v>97.9</v>
       </c>
-      <c r="W67" s="33"/>
-      <c r="X67" s="33"/>
+      <c r="W67" s="35"/>
+      <c r="X67" s="35"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
+      <c r="A68" s="32" t="s">
         <v>466</v>
       </c>
-      <c r="B68" s="33"/>
-      <c r="C68" s="33"/>
-      <c r="D68" s="33"/>
-      <c r="E68" s="31">
+      <c r="B68" s="35"/>
+      <c r="C68" s="35"/>
+      <c r="D68" s="35"/>
+      <c r="E68" s="33">
         <v>226.52</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="34">
         <v>41.23</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="33">
         <v>365.99</v>
       </c>
-      <c r="H68" s="33"/>
-      <c r="I68" s="33"/>
-      <c r="J68" s="33"/>
-      <c r="K68" s="32">
+      <c r="H68" s="35"/>
+      <c r="I68" s="35"/>
+      <c r="J68" s="35"/>
+      <c r="K68" s="34">
         <v>25.77</v>
       </c>
-      <c r="L68" s="31">
+      <c r="L68" s="33">
         <v>166.54</v>
       </c>
-      <c r="M68" s="33"/>
-      <c r="N68" s="33"/>
-      <c r="O68" s="33"/>
-      <c r="P68" s="33"/>
-      <c r="Q68" s="33"/>
-      <c r="R68" s="33"/>
-      <c r="S68" s="33"/>
-      <c r="T68" s="33"/>
-      <c r="U68" s="33"/>
-      <c r="V68" s="33"/>
-      <c r="W68" s="33"/>
-      <c r="X68" s="33"/>
+      <c r="M68" s="35"/>
+      <c r="N68" s="35"/>
+      <c r="O68" s="35"/>
+      <c r="P68" s="35"/>
+      <c r="Q68" s="35"/>
+      <c r="R68" s="35"/>
+      <c r="S68" s="35"/>
+      <c r="T68" s="35"/>
+      <c r="U68" s="35"/>
+      <c r="V68" s="35"/>
+      <c r="W68" s="35"/>
+      <c r="X68" s="35"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="28" t="s">
+      <c r="A69" s="30" t="s">
         <v>467</v>
       </c>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="29"/>
-      <c r="I69" s="29"/>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
-      <c r="L69" s="29"/>
-      <c r="M69" s="29"/>
-      <c r="N69" s="29"/>
-      <c r="O69" s="29"/>
-      <c r="P69" s="29"/>
-      <c r="Q69" s="29"/>
-      <c r="R69" s="29"/>
-      <c r="S69" s="29"/>
-      <c r="T69" s="29"/>
-      <c r="U69" s="29"/>
-      <c r="V69" s="29"/>
-      <c r="W69" s="29"/>
-      <c r="X69" s="29"/>
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="31"/>
+      <c r="F69" s="31"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="31"/>
+      <c r="I69" s="31"/>
+      <c r="J69" s="31"/>
+      <c r="K69" s="31"/>
+      <c r="L69" s="31"/>
+      <c r="M69" s="31"/>
+      <c r="N69" s="31"/>
+      <c r="O69" s="31"/>
+      <c r="P69" s="31"/>
+      <c r="Q69" s="31"/>
+      <c r="R69" s="31"/>
+      <c r="S69" s="31"/>
+      <c r="T69" s="31"/>
+      <c r="U69" s="31"/>
+      <c r="V69" s="31"/>
+      <c r="W69" s="31"/>
+      <c r="X69" s="31"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="30" t="s">
+      <c r="A70" s="32" t="s">
         <v>468</v>
       </c>
-      <c r="B70" s="33"/>
-      <c r="C70" s="33"/>
-      <c r="D70" s="32">
+      <c r="B70" s="35"/>
+      <c r="C70" s="35"/>
+      <c r="D70" s="34">
         <v>63.39</v>
       </c>
-      <c r="E70" s="33"/>
-      <c r="F70" s="33"/>
-      <c r="G70" s="32">
+      <c r="E70" s="35"/>
+      <c r="F70" s="35"/>
+      <c r="G70" s="34">
         <v>35.43</v>
       </c>
-      <c r="H70" s="32">
+      <c r="H70" s="34">
         <v>8.31</v>
       </c>
-      <c r="I70" s="32">
+      <c r="I70" s="34">
         <v>2.9</v>
       </c>
-      <c r="J70" s="33"/>
-      <c r="K70" s="33"/>
-      <c r="L70" s="33"/>
-      <c r="M70" s="33"/>
-      <c r="N70" s="32">
+      <c r="J70" s="35"/>
+      <c r="K70" s="35"/>
+      <c r="L70" s="35"/>
+      <c r="M70" s="35"/>
+      <c r="N70" s="34">
         <v>36.73</v>
       </c>
-      <c r="O70" s="32">
+      <c r="O70" s="34">
         <v>1.17</v>
       </c>
-      <c r="P70" s="33"/>
-      <c r="Q70" s="33"/>
-      <c r="R70" s="33"/>
-      <c r="S70" s="33"/>
-      <c r="T70" s="33"/>
-      <c r="U70" s="33"/>
-      <c r="V70" s="33"/>
-      <c r="W70" s="33"/>
-      <c r="X70" s="33"/>
+      <c r="P70" s="35"/>
+      <c r="Q70" s="35"/>
+      <c r="R70" s="35"/>
+      <c r="S70" s="35"/>
+      <c r="T70" s="35"/>
+      <c r="U70" s="35"/>
+      <c r="V70" s="35"/>
+      <c r="W70" s="35"/>
+      <c r="X70" s="35"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
+      <c r="A71" s="32" t="s">
         <v>469</v>
       </c>
-      <c r="B71" s="33"/>
-      <c r="C71" s="33"/>
-      <c r="D71" s="33"/>
-      <c r="E71" s="31">
+      <c r="B71" s="35"/>
+      <c r="C71" s="35"/>
+      <c r="D71" s="35"/>
+      <c r="E71" s="33">
         <v>598.36</v>
       </c>
-      <c r="F71" s="32">
+      <c r="F71" s="34">
         <v>41.23</v>
       </c>
-      <c r="G71" s="31">
+      <c r="G71" s="33">
         <v>365.99</v>
       </c>
-      <c r="H71" s="33"/>
-      <c r="I71" s="33"/>
-      <c r="J71" s="33"/>
-      <c r="K71" s="32">
+      <c r="H71" s="35"/>
+      <c r="I71" s="35"/>
+      <c r="J71" s="35"/>
+      <c r="K71" s="34">
         <v>36.6</v>
       </c>
-      <c r="L71" s="33"/>
-      <c r="M71" s="33"/>
-      <c r="N71" s="33"/>
-      <c r="O71" s="33"/>
-      <c r="P71" s="33"/>
-      <c r="Q71" s="33"/>
-      <c r="R71" s="33"/>
-      <c r="S71" s="33"/>
-      <c r="T71" s="33"/>
-      <c r="U71" s="33"/>
-      <c r="V71" s="33"/>
-      <c r="W71" s="33"/>
-      <c r="X71" s="33"/>
+      <c r="L71" s="35"/>
+      <c r="M71" s="35"/>
+      <c r="N71" s="35"/>
+      <c r="O71" s="35"/>
+      <c r="P71" s="35"/>
+      <c r="Q71" s="35"/>
+      <c r="R71" s="35"/>
+      <c r="S71" s="35"/>
+      <c r="T71" s="35"/>
+      <c r="U71" s="35"/>
+      <c r="V71" s="35"/>
+      <c r="W71" s="35"/>
+      <c r="X71" s="35"/>
     </row>
     <row r="72" ht="15.75" customHeight="1"/>
     <row r="73" ht="15.75" customHeight="1"/>
